--- a/artfynd/A 10555-2025 artfynd.xlsx
+++ b/artfynd/A 10555-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123878216</v>
+        <v>123878327</v>
       </c>
       <c r="B2" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>564936</v>
+        <v>564933</v>
       </c>
       <c r="R2" t="n">
-        <v>6443067</v>
+        <v>6443065</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123878867</v>
+        <v>123878808</v>
       </c>
       <c r="B3" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -917,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123878394</v>
+        <v>123879901</v>
       </c>
       <c r="B4" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -950,26 +950,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>564933</v>
+        <v>564839</v>
       </c>
       <c r="R4" t="n">
-        <v>6443065</v>
+        <v>6443048</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1001,7 +992,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1011,7 +1002,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123879901</v>
+        <v>123879049</v>
       </c>
       <c r="B5" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1071,17 +1062,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>564839</v>
+        <v>564930</v>
       </c>
       <c r="R5" t="n">
-        <v>6443048</v>
+        <v>6443013</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1150,10 +1150,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123878490</v>
+        <v>123879154</v>
       </c>
       <c r="B6" t="n">
-        <v>57860</v>
+        <v>98504</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1162,25 +1162,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1190,13 +1190,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>564933</v>
+        <v>564947</v>
       </c>
       <c r="R6" t="n">
-        <v>6443065</v>
+        <v>6443012</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1262,10 +1262,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123879942</v>
+        <v>123878450</v>
       </c>
       <c r="B7" t="n">
-        <v>98502</v>
+        <v>57644</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1274,35 +1274,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1311,13 +1307,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564852</v>
+        <v>564933</v>
       </c>
       <c r="R7" t="n">
-        <v>6443050</v>
+        <v>6443065</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1346,7 +1342,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1356,7 +1352,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1383,10 +1379,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123880241</v>
+        <v>123879288</v>
       </c>
       <c r="B8" t="n">
-        <v>98502</v>
+        <v>57507</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1395,50 +1391,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564938</v>
+        <v>564960</v>
       </c>
       <c r="R8" t="n">
-        <v>6443106</v>
+        <v>6443030</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1467,7 +1454,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1477,7 +1464,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1504,10 +1491,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123878450</v>
+        <v>123879574</v>
       </c>
       <c r="B9" t="n">
-        <v>57643</v>
+        <v>98504</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1516,31 +1503,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1549,13 +1540,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>564933</v>
+        <v>564879</v>
       </c>
       <c r="R9" t="n">
-        <v>6443065</v>
+        <v>6443023</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1584,7 +1575,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1594,7 +1585,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1621,10 +1612,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123878969</v>
+        <v>123879942</v>
       </c>
       <c r="B10" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1656,7 +1647,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1670,13 +1661,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>564923</v>
+        <v>564852</v>
       </c>
       <c r="R10" t="n">
-        <v>6443028</v>
+        <v>6443050</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1705,7 +1696,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1715,7 +1706,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1742,10 +1733,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123879154</v>
+        <v>123880057</v>
       </c>
       <c r="B11" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1775,20 +1766,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>564947</v>
+        <v>564855</v>
       </c>
       <c r="R11" t="n">
-        <v>6443012</v>
+        <v>6443055</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1857,7 +1857,7 @@
         <v>123879826</v>
       </c>
       <c r="B12" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1975,10 +1975,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123879656</v>
+        <v>123878969</v>
       </c>
       <c r="B13" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2024,13 +2024,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>564864</v>
+        <v>564923</v>
       </c>
       <c r="R13" t="n">
-        <v>6443040</v>
+        <v>6443028</v>
       </c>
       <c r="S13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2096,10 +2096,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123879288</v>
+        <v>123878885</v>
       </c>
       <c r="B14" t="n">
-        <v>57506</v>
+        <v>98504</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2108,41 +2108,50 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>564960</v>
+        <v>564921</v>
       </c>
       <c r="R14" t="n">
-        <v>6443030</v>
+        <v>6443041</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2171,7 +2180,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2181,7 +2190,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2208,10 +2217,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123880057</v>
+        <v>123879278</v>
       </c>
       <c r="B15" t="n">
-        <v>98502</v>
+        <v>105520</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2220,50 +2229,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>564855</v>
+        <v>564960</v>
       </c>
       <c r="R15" t="n">
-        <v>6443055</v>
+        <v>6443030</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2329,10 +2329,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123879867</v>
+        <v>123880241</v>
       </c>
       <c r="B16" t="n">
-        <v>105518</v>
+        <v>98504</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2341,38 +2341,47 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>564844</v>
+        <v>564938</v>
       </c>
       <c r="R16" t="n">
-        <v>6443043</v>
+        <v>6443106</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2404,7 +2413,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2414,7 +2423,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2441,10 +2450,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123879049</v>
+        <v>123879656</v>
       </c>
       <c r="B17" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2476,7 +2485,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2490,13 +2499,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>564930</v>
+        <v>564864</v>
       </c>
       <c r="R17" t="n">
-        <v>6443013</v>
+        <v>6443040</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2525,7 +2534,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2535,7 +2544,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2562,10 +2571,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123879278</v>
+        <v>123878216</v>
       </c>
       <c r="B18" t="n">
-        <v>105518</v>
+        <v>98504</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2574,38 +2583,47 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>564960</v>
+        <v>564936</v>
       </c>
       <c r="R18" t="n">
-        <v>6443030</v>
+        <v>6443067</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2637,7 +2655,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2647,7 +2665,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2674,10 +2692,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123879574</v>
+        <v>123878116</v>
       </c>
       <c r="B19" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2709,7 +2727,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2723,13 +2741,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>564879</v>
+        <v>564947</v>
       </c>
       <c r="R19" t="n">
-        <v>6443023</v>
+        <v>6443069</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2758,7 +2776,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2768,7 +2786,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2795,10 +2813,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123878885</v>
+        <v>123879729</v>
       </c>
       <c r="B20" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2830,7 +2848,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2844,13 +2862,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>564921</v>
+        <v>564847</v>
       </c>
       <c r="R20" t="n">
-        <v>6443041</v>
+        <v>6443048</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2879,7 +2897,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2889,7 +2907,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2916,10 +2934,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123878116</v>
+        <v>123878490</v>
       </c>
       <c r="B21" t="n">
-        <v>98502</v>
+        <v>57861</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2928,50 +2946,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>564947</v>
+        <v>564933</v>
       </c>
       <c r="R21" t="n">
-        <v>6443069</v>
+        <v>6443065</v>
       </c>
       <c r="S21" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3000,7 +3009,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3010,7 +3019,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3037,10 +3046,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123879729</v>
+        <v>123879867</v>
       </c>
       <c r="B22" t="n">
-        <v>98502</v>
+        <v>105520</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3049,47 +3058,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>564847</v>
+        <v>564844</v>
       </c>
       <c r="R22" t="n">
-        <v>6443048</v>
+        <v>6443043</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3155,6 +3155,730 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>123931335</v>
+      </c>
+      <c r="B23" t="n">
+        <v>98504</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>St Ved a10555, St Ved a10555, Sm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>564906</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6443033</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Gärdserum</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Björn Stenberg</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Björn Stenberg</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>123931662</v>
+      </c>
+      <c r="B24" t="n">
+        <v>98504</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>St Ved a10555, St Ved a10555, Sm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>564941</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6443068</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Gärdserum</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Björn Stenberg</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Björn Stenberg</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>123932083</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57644</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>St Ved a10555, St Ved a10555, Sm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>564954</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6443052</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Gärdserum</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Björn Stenberg</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Björn Stenberg</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>123931935</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57507</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>St Ved a10555, St Ved a10555, Sm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>564955</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6443078</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Gärdserum</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Björn Stenberg</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Björn Stenberg</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>123932605</v>
+      </c>
+      <c r="B27" t="n">
+        <v>98504</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>St Ved a10555, St Ved a10555, Sm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>564936</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6443071</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Gärdserum</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Björn Stenberg</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Björn Stenberg</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>123931443</v>
+      </c>
+      <c r="B28" t="n">
+        <v>98504</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>St Ved a10555, St Ved a10555, Sm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>564864</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6443083</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Gärdserum</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Björn Stenberg</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Björn Stenberg</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 10555-2025 artfynd.xlsx
+++ b/artfynd/A 10555-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123878327</v>
+        <v>123878808</v>
       </c>
       <c r="B2" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>564933</v>
+        <v>564916</v>
       </c>
       <c r="R2" t="n">
-        <v>6443065</v>
+        <v>6443042</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123878808</v>
+        <v>123879729</v>
       </c>
       <c r="B3" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -845,13 +845,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>564916</v>
+        <v>564847</v>
       </c>
       <c r="R3" t="n">
-        <v>6443042</v>
+        <v>6443048</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123879901</v>
+        <v>123879826</v>
       </c>
       <c r="B4" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -950,17 +950,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>564839</v>
+        <v>564844</v>
       </c>
       <c r="R4" t="n">
-        <v>6443048</v>
+        <v>6443043</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1029,10 +1038,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123879049</v>
+        <v>123878394</v>
       </c>
       <c r="B5" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1064,7 +1073,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1078,10 +1087,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>564930</v>
+        <v>564933</v>
       </c>
       <c r="R5" t="n">
-        <v>6443013</v>
+        <v>6443065</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1113,7 +1122,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1123,7 +1132,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1150,10 +1159,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123879154</v>
+        <v>123879288</v>
       </c>
       <c r="B6" t="n">
-        <v>98504</v>
+        <v>57507</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1162,25 +1171,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1190,13 +1199,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>564947</v>
+        <v>564960</v>
       </c>
       <c r="R6" t="n">
-        <v>6443012</v>
+        <v>6443030</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1225,7 +1234,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1235,7 +1244,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1262,10 +1271,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123878450</v>
+        <v>123879130</v>
       </c>
       <c r="B7" t="n">
-        <v>57644</v>
+        <v>98079</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1274,46 +1283,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564933</v>
+        <v>564947</v>
       </c>
       <c r="R7" t="n">
-        <v>6443065</v>
+        <v>6443012</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1342,7 +1346,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1352,7 +1356,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1379,10 +1383,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123879288</v>
+        <v>123878116</v>
       </c>
       <c r="B8" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1391,41 +1395,50 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564960</v>
+        <v>564947</v>
       </c>
       <c r="R8" t="n">
-        <v>6443030</v>
+        <v>6443069</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1454,7 +1467,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1464,7 +1477,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1491,10 +1504,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123879574</v>
+        <v>123879656</v>
       </c>
       <c r="B9" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1526,7 +1539,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1540,13 +1553,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>564879</v>
+        <v>564864</v>
       </c>
       <c r="R9" t="n">
-        <v>6443023</v>
+        <v>6443040</v>
       </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1575,7 +1588,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1585,7 +1598,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1612,10 +1625,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123879942</v>
+        <v>123879049</v>
       </c>
       <c r="B10" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1647,7 +1660,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1661,13 +1674,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>564852</v>
+        <v>564930</v>
       </c>
       <c r="R10" t="n">
-        <v>6443050</v>
+        <v>6443013</v>
       </c>
       <c r="S10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1696,7 +1709,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1706,7 +1719,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1733,10 +1746,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123880057</v>
+        <v>123879942</v>
       </c>
       <c r="B11" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1768,7 +1781,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1782,13 +1795,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>564855</v>
+        <v>564852</v>
       </c>
       <c r="R11" t="n">
-        <v>6443055</v>
+        <v>6443050</v>
       </c>
       <c r="S11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1854,10 +1867,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123879826</v>
+        <v>123880241</v>
       </c>
       <c r="B12" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1889,7 +1902,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1903,10 +1916,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>564844</v>
+        <v>564938</v>
       </c>
       <c r="R12" t="n">
-        <v>6443043</v>
+        <v>6443106</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1938,7 +1951,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1948,7 +1961,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1978,7 +1991,7 @@
         <v>123878969</v>
       </c>
       <c r="B13" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2096,10 +2109,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123878885</v>
+        <v>123879901</v>
       </c>
       <c r="B14" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2129,29 +2142,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>564921</v>
+        <v>564839</v>
       </c>
       <c r="R14" t="n">
-        <v>6443041</v>
+        <v>6443048</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2180,7 +2184,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2190,7 +2194,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2220,7 +2224,7 @@
         <v>123879278</v>
       </c>
       <c r="B15" t="n">
-        <v>105520</v>
+        <v>105095</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2329,10 +2333,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123880241</v>
+        <v>123878490</v>
       </c>
       <c r="B16" t="n">
-        <v>98504</v>
+        <v>57861</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2341,50 +2345,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>564938</v>
+        <v>564933</v>
       </c>
       <c r="R16" t="n">
-        <v>6443106</v>
+        <v>6443065</v>
       </c>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2413,7 +2408,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2423,7 +2418,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2450,10 +2445,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123879656</v>
+        <v>123878450</v>
       </c>
       <c r="B17" t="n">
-        <v>98504</v>
+        <v>57644</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2462,35 +2457,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2499,13 +2490,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>564864</v>
+        <v>564933</v>
       </c>
       <c r="R17" t="n">
-        <v>6443040</v>
+        <v>6443065</v>
       </c>
       <c r="S17" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2534,7 +2525,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2544,7 +2535,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2571,10 +2562,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123878216</v>
+        <v>123879867</v>
       </c>
       <c r="B18" t="n">
-        <v>98504</v>
+        <v>105095</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2583,47 +2574,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>564936</v>
+        <v>564844</v>
       </c>
       <c r="R18" t="n">
-        <v>6443067</v>
+        <v>6443043</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2655,7 +2637,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2665,7 +2647,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2692,10 +2674,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123878116</v>
+        <v>123880057</v>
       </c>
       <c r="B19" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2727,7 +2709,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2741,13 +2723,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>564947</v>
+        <v>564855</v>
       </c>
       <c r="R19" t="n">
-        <v>6443069</v>
+        <v>6443055</v>
       </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2776,7 +2758,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2786,7 +2768,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2813,10 +2795,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123879729</v>
+        <v>123879574</v>
       </c>
       <c r="B20" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2848,7 +2830,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2862,13 +2844,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>564847</v>
+        <v>564879</v>
       </c>
       <c r="R20" t="n">
-        <v>6443048</v>
+        <v>6443023</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2897,7 +2879,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2907,7 +2889,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2934,10 +2916,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123878490</v>
+        <v>123878885</v>
       </c>
       <c r="B21" t="n">
-        <v>57861</v>
+        <v>98079</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2946,41 +2928,50 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>564933</v>
+        <v>564921</v>
       </c>
       <c r="R21" t="n">
-        <v>6443065</v>
+        <v>6443041</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3009,7 +3000,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3019,7 +3010,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3046,10 +3037,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123879867</v>
+        <v>123878216</v>
       </c>
       <c r="B22" t="n">
-        <v>105520</v>
+        <v>98079</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3058,38 +3049,47 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>564844</v>
+        <v>564936</v>
       </c>
       <c r="R22" t="n">
-        <v>6443043</v>
+        <v>6443067</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3158,10 +3158,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123931335</v>
+        <v>123931935</v>
       </c>
       <c r="B23" t="n">
-        <v>98504</v>
+        <v>57507</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3170,35 +3170,39 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3206,10 +3210,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>564906</v>
+        <v>564955</v>
       </c>
       <c r="R23" t="n">
-        <v>6443033</v>
+        <v>6443078</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3241,7 +3245,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3251,7 +3255,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3260,7 +3264,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3279,10 +3282,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123931662</v>
+        <v>123931335</v>
       </c>
       <c r="B24" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3314,7 +3317,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
@@ -3327,10 +3330,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>564941</v>
+        <v>564906</v>
       </c>
       <c r="R24" t="n">
-        <v>6443068</v>
+        <v>6443033</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3362,7 +3365,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3372,7 +3375,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3400,10 +3403,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123932083</v>
+        <v>123931443</v>
       </c>
       <c r="B25" t="n">
-        <v>57644</v>
+        <v>98079</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3412,50 +3415,49 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>St Ved a10555, St Ved a10555, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>564954</v>
+        <v>564864</v>
       </c>
       <c r="R25" t="n">
-        <v>6443052</v>
+        <v>6443083</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3484,7 +3486,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3494,7 +3496,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3503,6 +3505,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3521,10 +3524,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123931935</v>
+        <v>123931662</v>
       </c>
       <c r="B26" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3533,39 +3536,35 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3573,10 +3572,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>564955</v>
+        <v>564941</v>
       </c>
       <c r="R26" t="n">
-        <v>6443078</v>
+        <v>6443068</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3608,7 +3607,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3618,7 +3617,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3627,6 +3626,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3648,7 +3648,7 @@
         <v>123932605</v>
       </c>
       <c r="B27" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3761,10 +3761,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123931443</v>
+        <v>123932083</v>
       </c>
       <c r="B28" t="n">
-        <v>98504</v>
+        <v>57644</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3773,49 +3773,50 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>St Ved a10555, St Ved a10555, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>564864</v>
+        <v>564954</v>
       </c>
       <c r="R28" t="n">
-        <v>6443083</v>
+        <v>6443052</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3844,7 +3845,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3854,7 +3855,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3863,7 +3864,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 10555-2025 artfynd.xlsx
+++ b/artfynd/A 10555-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123878808</v>
+        <v>123878852</v>
       </c>
       <c r="B2" t="n">
         <v>98079</v>
@@ -796,7 +796,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123879729</v>
+        <v>123879656</v>
       </c>
       <c r="B3" t="n">
         <v>98079</v>
@@ -831,7 +831,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -845,13 +845,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>564847</v>
+        <v>564864</v>
       </c>
       <c r="R3" t="n">
-        <v>6443048</v>
+        <v>6443040</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123879826</v>
+        <v>123878216</v>
       </c>
       <c r="B4" t="n">
         <v>98079</v>
@@ -952,7 +952,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -966,10 +966,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>564844</v>
+        <v>564936</v>
       </c>
       <c r="R4" t="n">
-        <v>6443043</v>
+        <v>6443067</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,7 +1038,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123878394</v>
+        <v>123879826</v>
       </c>
       <c r="B5" t="n">
         <v>98079</v>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>564933</v>
+        <v>564844</v>
       </c>
       <c r="R5" t="n">
-        <v>6443065</v>
+        <v>6443043</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,10 +1159,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123879288</v>
+        <v>123880241</v>
       </c>
       <c r="B6" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1171,41 +1171,50 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>564960</v>
+        <v>564938</v>
       </c>
       <c r="R6" t="n">
-        <v>6443030</v>
+        <v>6443106</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1234,7 +1243,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1244,7 +1253,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1271,7 +1280,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123879130</v>
+        <v>123879154</v>
       </c>
       <c r="B7" t="n">
         <v>98079</v>
@@ -1346,7 +1355,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1356,7 +1365,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1383,10 +1392,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123878116</v>
+        <v>123878450</v>
       </c>
       <c r="B8" t="n">
-        <v>98079</v>
+        <v>57644</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1395,35 +1404,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1432,13 +1437,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564947</v>
+        <v>564933</v>
       </c>
       <c r="R8" t="n">
-        <v>6443069</v>
+        <v>6443065</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1467,7 +1472,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1477,7 +1482,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1504,7 +1509,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123879656</v>
+        <v>123879049</v>
       </c>
       <c r="B9" t="n">
         <v>98079</v>
@@ -1539,7 +1544,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1553,13 +1558,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>564864</v>
+        <v>564930</v>
       </c>
       <c r="R9" t="n">
-        <v>6443040</v>
+        <v>6443013</v>
       </c>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1588,7 +1593,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1598,7 +1603,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1625,7 +1630,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123879049</v>
+        <v>123879574</v>
       </c>
       <c r="B10" t="n">
         <v>98079</v>
@@ -1660,7 +1665,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1674,13 +1679,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>564930</v>
+        <v>564879</v>
       </c>
       <c r="R10" t="n">
-        <v>6443013</v>
+        <v>6443023</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1709,7 +1714,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1719,7 +1724,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1746,7 +1751,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123879942</v>
+        <v>123878394</v>
       </c>
       <c r="B11" t="n">
         <v>98079</v>
@@ -1781,7 +1786,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1795,13 +1800,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>564852</v>
+        <v>564933</v>
       </c>
       <c r="R11" t="n">
-        <v>6443050</v>
+        <v>6443065</v>
       </c>
       <c r="S11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1830,7 +1835,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1840,7 +1845,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1867,7 +1872,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123880241</v>
+        <v>123879901</v>
       </c>
       <c r="B12" t="n">
         <v>98079</v>
@@ -1900,26 +1905,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>564938</v>
+        <v>564839</v>
       </c>
       <c r="R12" t="n">
-        <v>6443106</v>
+        <v>6443048</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1951,7 +1947,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1961,7 +1957,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1988,10 +1984,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123878969</v>
+        <v>123879278</v>
       </c>
       <c r="B13" t="n">
-        <v>98079</v>
+        <v>105095</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2000,47 +1996,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>564923</v>
+        <v>564960</v>
       </c>
       <c r="R13" t="n">
-        <v>6443028</v>
+        <v>6443030</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -2072,7 +2059,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2082,7 +2069,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2109,10 +2096,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123879901</v>
+        <v>123879288</v>
       </c>
       <c r="B14" t="n">
-        <v>98079</v>
+        <v>57507</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2121,25 +2108,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2149,13 +2136,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>564839</v>
+        <v>564960</v>
       </c>
       <c r="R14" t="n">
-        <v>6443048</v>
+        <v>6443030</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2184,7 +2171,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2194,7 +2181,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2221,10 +2208,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123879278</v>
+        <v>123878490</v>
       </c>
       <c r="B15" t="n">
-        <v>105095</v>
+        <v>57861</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2237,21 +2224,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221144</v>
+        <v>103015</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2261,13 +2248,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>564960</v>
+        <v>564933</v>
       </c>
       <c r="R15" t="n">
-        <v>6443030</v>
+        <v>6443065</v>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2296,7 +2283,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2306,7 +2293,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2333,10 +2320,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123878490</v>
+        <v>123879729</v>
       </c>
       <c r="B16" t="n">
-        <v>57861</v>
+        <v>98079</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2345,41 +2332,50 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>564933</v>
+        <v>564847</v>
       </c>
       <c r="R16" t="n">
-        <v>6443065</v>
+        <v>6443048</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2408,7 +2404,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2418,7 +2414,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2445,10 +2441,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123878450</v>
+        <v>123878885</v>
       </c>
       <c r="B17" t="n">
-        <v>57644</v>
+        <v>98079</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2457,31 +2453,35 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2490,13 +2490,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>564933</v>
+        <v>564921</v>
       </c>
       <c r="R17" t="n">
-        <v>6443065</v>
+        <v>6443041</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2535,7 +2535,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2674,7 +2674,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123880057</v>
+        <v>123878116</v>
       </c>
       <c r="B19" t="n">
         <v>98079</v>
@@ -2709,7 +2709,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2723,13 +2723,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>564855</v>
+        <v>564947</v>
       </c>
       <c r="R19" t="n">
-        <v>6443055</v>
+        <v>6443069</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2795,7 +2795,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123879574</v>
+        <v>123879942</v>
       </c>
       <c r="B20" t="n">
         <v>98079</v>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2844,13 +2844,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>564879</v>
+        <v>564852</v>
       </c>
       <c r="R20" t="n">
-        <v>6443023</v>
+        <v>6443050</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2889,7 +2889,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2916,7 +2916,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123878885</v>
+        <v>123880057</v>
       </c>
       <c r="B21" t="n">
         <v>98079</v>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2965,13 +2965,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>564921</v>
+        <v>564855</v>
       </c>
       <c r="R21" t="n">
-        <v>6443041</v>
+        <v>6443055</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3010,7 +3010,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3037,7 +3037,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123878216</v>
+        <v>123878969</v>
       </c>
       <c r="B22" t="n">
         <v>98079</v>
@@ -3072,7 +3072,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3086,10 +3086,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>564936</v>
+        <v>564923</v>
       </c>
       <c r="R22" t="n">
-        <v>6443067</v>
+        <v>6443028</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3158,10 +3158,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123931935</v>
+        <v>123931443</v>
       </c>
       <c r="B23" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3170,39 +3170,35 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3210,10 +3206,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>564955</v>
+        <v>564864</v>
       </c>
       <c r="R23" t="n">
-        <v>6443078</v>
+        <v>6443083</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3245,7 +3241,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3255,7 +3251,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3264,6 +3260,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3403,10 +3400,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123931443</v>
+        <v>123931935</v>
       </c>
       <c r="B25" t="n">
-        <v>98079</v>
+        <v>57507</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3415,35 +3412,39 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3451,10 +3452,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>564864</v>
+        <v>564955</v>
       </c>
       <c r="R25" t="n">
-        <v>6443083</v>
+        <v>6443078</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3486,7 +3487,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3496,7 +3497,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3505,7 +3506,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3524,7 +3524,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123931662</v>
+        <v>123932605</v>
       </c>
       <c r="B26" t="n">
         <v>98079</v>
@@ -3559,23 +3559,19 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>St Ved a10555, St Ved a10555, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>564941</v>
+        <v>564936</v>
       </c>
       <c r="R26" t="n">
-        <v>6443068</v>
+        <v>6443071</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3607,7 +3603,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3617,7 +3613,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3626,7 +3622,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3645,7 +3640,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123932605</v>
+        <v>123931662</v>
       </c>
       <c r="B27" t="n">
         <v>98079</v>
@@ -3680,19 +3675,23 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>St Ved a10555, St Ved a10555, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>564936</v>
+        <v>564941</v>
       </c>
       <c r="R27" t="n">
-        <v>6443071</v>
+        <v>6443068</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3724,7 +3723,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3734,7 +3733,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3743,6 +3742,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 10555-2025 artfynd.xlsx
+++ b/artfynd/A 10555-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123878852</v>
+        <v>123879942</v>
       </c>
       <c r="B2" t="n">
         <v>98079</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>564916</v>
+        <v>564852</v>
       </c>
       <c r="R2" t="n">
-        <v>6443042</v>
+        <v>6443050</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,7 +796,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123879656</v>
+        <v>123878969</v>
       </c>
       <c r="B3" t="n">
         <v>98079</v>
@@ -831,7 +831,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -845,13 +845,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>564864</v>
+        <v>564923</v>
       </c>
       <c r="R3" t="n">
-        <v>6443040</v>
+        <v>6443028</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,7 +917,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123878216</v>
+        <v>123879574</v>
       </c>
       <c r="B4" t="n">
         <v>98079</v>
@@ -952,7 +952,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -966,13 +966,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>564936</v>
+        <v>564879</v>
       </c>
       <c r="R4" t="n">
-        <v>6443067</v>
+        <v>6443023</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,10 +1038,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123879826</v>
+        <v>123878450</v>
       </c>
       <c r="B5" t="n">
-        <v>98079</v>
+        <v>57644</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1050,35 +1050,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1087,13 +1083,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>564844</v>
+        <v>564933</v>
       </c>
       <c r="R5" t="n">
-        <v>6443043</v>
+        <v>6443065</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1122,7 +1118,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1132,7 +1128,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1280,7 +1276,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123879154</v>
+        <v>123879130</v>
       </c>
       <c r="B7" t="n">
         <v>98079</v>
@@ -1355,7 +1351,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1365,7 +1361,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1392,10 +1388,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123878450</v>
+        <v>123880057</v>
       </c>
       <c r="B8" t="n">
-        <v>57644</v>
+        <v>98079</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1404,31 +1400,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1437,13 +1437,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564933</v>
+        <v>564855</v>
       </c>
       <c r="R8" t="n">
-        <v>6443065</v>
+        <v>6443055</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1509,10 +1509,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123879049</v>
+        <v>123879288</v>
       </c>
       <c r="B9" t="n">
-        <v>98079</v>
+        <v>57507</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1521,50 +1521,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>564930</v>
+        <v>564960</v>
       </c>
       <c r="R9" t="n">
-        <v>6443013</v>
+        <v>6443030</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1593,7 +1584,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1603,7 +1594,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1630,7 +1621,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123879574</v>
+        <v>123878371</v>
       </c>
       <c r="B10" t="n">
         <v>98079</v>
@@ -1665,7 +1656,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1679,13 +1670,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>564879</v>
+        <v>564933</v>
       </c>
       <c r="R10" t="n">
-        <v>6443023</v>
+        <v>6443065</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1714,7 +1705,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1724,7 +1715,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1751,7 +1742,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123878394</v>
+        <v>123878867</v>
       </c>
       <c r="B11" t="n">
         <v>98079</v>
@@ -1786,7 +1777,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1800,13 +1791,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>564933</v>
+        <v>564916</v>
       </c>
       <c r="R11" t="n">
-        <v>6443065</v>
+        <v>6443042</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1835,7 +1826,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1845,7 +1836,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1872,7 +1863,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123879901</v>
+        <v>123879729</v>
       </c>
       <c r="B12" t="n">
         <v>98079</v>
@@ -1905,14 +1896,23 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>564839</v>
+        <v>564847</v>
       </c>
       <c r="R12" t="n">
         <v>6443048</v>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1984,10 +1984,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123879278</v>
+        <v>123878490</v>
       </c>
       <c r="B13" t="n">
-        <v>105095</v>
+        <v>57861</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2000,21 +2000,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221144</v>
+        <v>103015</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2024,13 +2024,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>564960</v>
+        <v>564933</v>
       </c>
       <c r="R13" t="n">
-        <v>6443030</v>
+        <v>6443065</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2096,10 +2096,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123879288</v>
+        <v>123879826</v>
       </c>
       <c r="B14" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2108,41 +2108,50 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>564960</v>
+        <v>564844</v>
       </c>
       <c r="R14" t="n">
-        <v>6443030</v>
+        <v>6443043</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2171,7 +2180,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2181,7 +2190,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2208,10 +2217,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123878490</v>
+        <v>123878885</v>
       </c>
       <c r="B15" t="n">
-        <v>57861</v>
+        <v>98079</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2220,41 +2229,50 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>564933</v>
+        <v>564921</v>
       </c>
       <c r="R15" t="n">
-        <v>6443065</v>
+        <v>6443041</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2283,7 +2301,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2293,7 +2311,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2320,7 +2338,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123879729</v>
+        <v>123879049</v>
       </c>
       <c r="B16" t="n">
         <v>98079</v>
@@ -2355,7 +2373,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2369,10 +2387,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>564847</v>
+        <v>564930</v>
       </c>
       <c r="R16" t="n">
-        <v>6443048</v>
+        <v>6443013</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2404,7 +2422,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2414,7 +2432,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2441,7 +2459,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123878885</v>
+        <v>123879901</v>
       </c>
       <c r="B17" t="n">
         <v>98079</v>
@@ -2474,29 +2492,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>564921</v>
+        <v>564839</v>
       </c>
       <c r="R17" t="n">
-        <v>6443041</v>
+        <v>6443048</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2525,7 +2534,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2535,7 +2544,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2562,10 +2571,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123879867</v>
+        <v>123878216</v>
       </c>
       <c r="B18" t="n">
-        <v>105095</v>
+        <v>98079</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2574,38 +2583,47 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>564844</v>
+        <v>564936</v>
       </c>
       <c r="R18" t="n">
-        <v>6443043</v>
+        <v>6443067</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2637,7 +2655,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2647,7 +2665,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2674,7 +2692,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123878116</v>
+        <v>123879656</v>
       </c>
       <c r="B19" t="n">
         <v>98079</v>
@@ -2709,7 +2727,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2723,13 +2741,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>564947</v>
+        <v>564864</v>
       </c>
       <c r="R19" t="n">
-        <v>6443069</v>
+        <v>6443040</v>
       </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2758,7 +2776,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2768,7 +2786,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2795,10 +2813,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123879942</v>
+        <v>123879867</v>
       </c>
       <c r="B20" t="n">
-        <v>98079</v>
+        <v>105095</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2807,50 +2825,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>564852</v>
+        <v>564844</v>
       </c>
       <c r="R20" t="n">
-        <v>6443050</v>
+        <v>6443043</v>
       </c>
       <c r="S20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2879,7 +2888,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2889,7 +2898,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2916,10 +2925,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123880057</v>
+        <v>123879278</v>
       </c>
       <c r="B21" t="n">
-        <v>98079</v>
+        <v>105095</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2928,50 +2937,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>564855</v>
+        <v>564960</v>
       </c>
       <c r="R21" t="n">
-        <v>6443055</v>
+        <v>6443030</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3010,7 +3010,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3037,7 +3037,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123878969</v>
+        <v>123878116</v>
       </c>
       <c r="B22" t="n">
         <v>98079</v>
@@ -3072,7 +3072,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3086,10 +3086,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>564923</v>
+        <v>564947</v>
       </c>
       <c r="R22" t="n">
-        <v>6443028</v>
+        <v>6443069</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 10555-2025 artfynd.xlsx
+++ b/artfynd/A 10555-2025 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123878969</v>
+        <v>123879288</v>
       </c>
       <c r="B3" t="n">
-        <v>98079</v>
+        <v>57507</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,50 +808,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>564923</v>
+        <v>564960</v>
       </c>
       <c r="R3" t="n">
-        <v>6443028</v>
+        <v>6443030</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,7 +908,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123879574</v>
+        <v>123879826</v>
       </c>
       <c r="B4" t="n">
         <v>98079</v>
@@ -952,7 +943,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -966,13 +957,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>564879</v>
+        <v>564844</v>
       </c>
       <c r="R4" t="n">
-        <v>6443023</v>
+        <v>6443043</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1001,7 +992,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1011,7 +1002,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123878450</v>
+        <v>123879867</v>
       </c>
       <c r="B5" t="n">
-        <v>57644</v>
+        <v>105095</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1050,46 +1041,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>564933</v>
+        <v>564844</v>
       </c>
       <c r="R5" t="n">
-        <v>6443065</v>
+        <v>6443043</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1118,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1128,7 +1114,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,7 +1141,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123880241</v>
+        <v>123878371</v>
       </c>
       <c r="B6" t="n">
         <v>98079</v>
@@ -1190,7 +1176,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1204,10 +1190,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>564938</v>
+        <v>564933</v>
       </c>
       <c r="R6" t="n">
-        <v>6443106</v>
+        <v>6443065</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1239,7 +1225,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1249,7 +1235,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1276,7 +1262,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123879130</v>
+        <v>123878804</v>
       </c>
       <c r="B7" t="n">
         <v>98079</v>
@@ -1309,20 +1295,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564947</v>
+        <v>564916</v>
       </c>
       <c r="R7" t="n">
-        <v>6443012</v>
+        <v>6443042</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1351,7 +1346,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1361,7 +1356,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1388,7 +1383,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123880057</v>
+        <v>123879130</v>
       </c>
       <c r="B8" t="n">
         <v>98079</v>
@@ -1421,29 +1416,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564855</v>
+        <v>564947</v>
       </c>
       <c r="R8" t="n">
-        <v>6443055</v>
+        <v>6443012</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1472,7 +1458,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1482,7 +1468,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1509,10 +1495,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123879288</v>
+        <v>123879278</v>
       </c>
       <c r="B9" t="n">
-        <v>57507</v>
+        <v>105095</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1521,25 +1507,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1555,7 +1541,7 @@
         <v>6443030</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1584,7 +1570,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1594,7 +1580,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1621,7 +1607,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123878371</v>
+        <v>123880241</v>
       </c>
       <c r="B10" t="n">
         <v>98079</v>
@@ -1656,7 +1642,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1670,10 +1656,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>564933</v>
+        <v>564938</v>
       </c>
       <c r="R10" t="n">
-        <v>6443065</v>
+        <v>6443106</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1705,7 +1691,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1715,7 +1701,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1742,10 +1728,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123878867</v>
+        <v>123878490</v>
       </c>
       <c r="B11" t="n">
-        <v>98079</v>
+        <v>57861</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1754,50 +1740,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>564916</v>
+        <v>564933</v>
       </c>
       <c r="R11" t="n">
-        <v>6443042</v>
+        <v>6443065</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1826,7 +1803,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1836,7 +1813,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1863,10 +1840,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123879729</v>
+        <v>123878450</v>
       </c>
       <c r="B12" t="n">
-        <v>98079</v>
+        <v>57644</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1875,35 +1852,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1912,13 +1885,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>564847</v>
+        <v>564933</v>
       </c>
       <c r="R12" t="n">
-        <v>6443048</v>
+        <v>6443065</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1947,7 +1920,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1957,7 +1930,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1984,10 +1957,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123878490</v>
+        <v>123878969</v>
       </c>
       <c r="B13" t="n">
-        <v>57861</v>
+        <v>98079</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1996,41 +1969,50 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>564933</v>
+        <v>564923</v>
       </c>
       <c r="R13" t="n">
-        <v>6443065</v>
+        <v>6443028</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2059,7 +2041,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2069,7 +2051,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2096,7 +2078,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123879826</v>
+        <v>123879729</v>
       </c>
       <c r="B14" t="n">
         <v>98079</v>
@@ -2131,7 +2113,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2145,10 +2127,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>564844</v>
+        <v>564847</v>
       </c>
       <c r="R14" t="n">
-        <v>6443043</v>
+        <v>6443048</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2180,7 +2162,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2190,7 +2172,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2217,7 +2199,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123878885</v>
+        <v>123880057</v>
       </c>
       <c r="B15" t="n">
         <v>98079</v>
@@ -2252,7 +2234,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2266,13 +2248,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>564921</v>
+        <v>564855</v>
       </c>
       <c r="R15" t="n">
-        <v>6443041</v>
+        <v>6443055</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2301,7 +2283,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2311,7 +2293,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2338,7 +2320,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123879049</v>
+        <v>123879574</v>
       </c>
       <c r="B16" t="n">
         <v>98079</v>
@@ -2373,7 +2355,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2387,13 +2369,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>564930</v>
+        <v>564879</v>
       </c>
       <c r="R16" t="n">
-        <v>6443013</v>
+        <v>6443023</v>
       </c>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2422,7 +2404,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2432,7 +2414,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2459,7 +2441,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123879901</v>
+        <v>123879049</v>
       </c>
       <c r="B17" t="n">
         <v>98079</v>
@@ -2492,17 +2474,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>564839</v>
+        <v>564930</v>
       </c>
       <c r="R17" t="n">
-        <v>6443048</v>
+        <v>6443013</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2534,7 +2525,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2544,7 +2535,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2571,7 +2562,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123878216</v>
+        <v>123879656</v>
       </c>
       <c r="B18" t="n">
         <v>98079</v>
@@ -2606,7 +2597,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2620,13 +2611,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>564936</v>
+        <v>564864</v>
       </c>
       <c r="R18" t="n">
-        <v>6443067</v>
+        <v>6443040</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2655,7 +2646,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2665,7 +2656,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2692,7 +2683,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123879656</v>
+        <v>123878216</v>
       </c>
       <c r="B19" t="n">
         <v>98079</v>
@@ -2727,7 +2718,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2741,13 +2732,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>564864</v>
+        <v>564936</v>
       </c>
       <c r="R19" t="n">
-        <v>6443040</v>
+        <v>6443067</v>
       </c>
       <c r="S19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2776,7 +2767,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2786,7 +2777,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2813,10 +2804,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123879867</v>
+        <v>123878116</v>
       </c>
       <c r="B20" t="n">
-        <v>105095</v>
+        <v>98079</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2825,38 +2816,47 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>564844</v>
+        <v>564947</v>
       </c>
       <c r="R20" t="n">
-        <v>6443043</v>
+        <v>6443069</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2888,7 +2888,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2925,10 +2925,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123879278</v>
+        <v>123879901</v>
       </c>
       <c r="B21" t="n">
-        <v>105095</v>
+        <v>98079</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2937,25 +2937,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>564960</v>
+        <v>564839</v>
       </c>
       <c r="R21" t="n">
-        <v>6443030</v>
+        <v>6443048</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3010,7 +3010,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3037,7 +3037,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123878116</v>
+        <v>123878885</v>
       </c>
       <c r="B22" t="n">
         <v>98079</v>
@@ -3072,7 +3072,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3086,13 +3086,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>564947</v>
+        <v>564921</v>
       </c>
       <c r="R22" t="n">
-        <v>6443069</v>
+        <v>6443041</v>
       </c>
       <c r="S22" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3158,7 +3158,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123931443</v>
+        <v>123931335</v>
       </c>
       <c r="B23" t="n">
         <v>98079</v>
@@ -3206,10 +3206,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>564864</v>
+        <v>564906</v>
       </c>
       <c r="R23" t="n">
-        <v>6443083</v>
+        <v>6443033</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3279,7 +3279,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123931335</v>
+        <v>123931443</v>
       </c>
       <c r="B24" t="n">
         <v>98079</v>
@@ -3327,10 +3327,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>564906</v>
+        <v>564864</v>
       </c>
       <c r="R24" t="n">
-        <v>6443033</v>
+        <v>6443083</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3362,7 +3362,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3372,7 +3372,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3400,10 +3400,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123931935</v>
+        <v>123932605</v>
       </c>
       <c r="B25" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3412,50 +3412,42 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>St Ved a10555, St Ved a10555, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>564955</v>
+        <v>564936</v>
       </c>
       <c r="R25" t="n">
-        <v>6443078</v>
+        <v>6443071</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3487,7 +3479,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3497,7 +3489,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3524,10 +3516,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123932605</v>
+        <v>123931935</v>
       </c>
       <c r="B26" t="n">
-        <v>98079</v>
+        <v>57507</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3536,42 +3528,50 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>St Ved a10555, St Ved a10555, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>564936</v>
+        <v>564955</v>
       </c>
       <c r="R26" t="n">
-        <v>6443071</v>
+        <v>6443078</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3603,7 +3603,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3613,7 +3613,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3640,10 +3640,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123931662</v>
+        <v>123932083</v>
       </c>
       <c r="B27" t="n">
-        <v>98079</v>
+        <v>57644</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3652,49 +3652,50 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>St Ved a10555, St Ved a10555, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>564941</v>
+        <v>564954</v>
       </c>
       <c r="R27" t="n">
-        <v>6443068</v>
+        <v>6443052</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3723,7 +3724,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3733,7 +3734,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3742,7 +3743,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3761,10 +3761,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123932083</v>
+        <v>123931662</v>
       </c>
       <c r="B28" t="n">
-        <v>57644</v>
+        <v>98079</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3773,50 +3773,49 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>St Ved a10555, St Ved a10555, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>564954</v>
+        <v>564941</v>
       </c>
       <c r="R28" t="n">
-        <v>6443052</v>
+        <v>6443068</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3845,7 +3844,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3855,7 +3854,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3864,6 +3863,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 10555-2025 artfynd.xlsx
+++ b/artfynd/A 10555-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123879942</v>
+        <v>123879867</v>
       </c>
       <c r="B2" t="n">
-        <v>98079</v>
+        <v>105095</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,50 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>564852</v>
+        <v>564844</v>
       </c>
       <c r="R2" t="n">
-        <v>6443050</v>
+        <v>6443043</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123879288</v>
+        <v>123878852</v>
       </c>
       <c r="B3" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,41 +799,50 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>564960</v>
+        <v>564916</v>
       </c>
       <c r="R3" t="n">
-        <v>6443030</v>
+        <v>6443042</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,7 +908,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123879826</v>
+        <v>123879656</v>
       </c>
       <c r="B4" t="n">
         <v>98079</v>
@@ -943,7 +943,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -957,13 +957,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>564844</v>
+        <v>564864</v>
       </c>
       <c r="R4" t="n">
-        <v>6443043</v>
+        <v>6443040</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123879867</v>
+        <v>123879288</v>
       </c>
       <c r="B5" t="n">
-        <v>105095</v>
+        <v>57507</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,25 +1041,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1069,13 +1069,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>564844</v>
+        <v>564960</v>
       </c>
       <c r="R5" t="n">
-        <v>6443043</v>
+        <v>6443030</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,7 +1141,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123878371</v>
+        <v>123879130</v>
       </c>
       <c r="B6" t="n">
         <v>98079</v>
@@ -1174,26 +1174,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>564933</v>
+        <v>564947</v>
       </c>
       <c r="R6" t="n">
-        <v>6443065</v>
+        <v>6443012</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1225,7 +1216,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1235,7 +1226,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1262,7 +1253,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123878804</v>
+        <v>123878371</v>
       </c>
       <c r="B7" t="n">
         <v>98079</v>
@@ -1297,7 +1288,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1311,13 +1302,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564916</v>
+        <v>564933</v>
       </c>
       <c r="R7" t="n">
-        <v>6443042</v>
+        <v>6443065</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1346,7 +1337,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1356,7 +1347,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1383,7 +1374,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123879130</v>
+        <v>123879049</v>
       </c>
       <c r="B8" t="n">
         <v>98079</v>
@@ -1416,17 +1407,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564947</v>
+        <v>564930</v>
       </c>
       <c r="R8" t="n">
-        <v>6443012</v>
+        <v>6443013</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1495,10 +1495,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123879278</v>
+        <v>123879826</v>
       </c>
       <c r="B9" t="n">
-        <v>105095</v>
+        <v>98079</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1507,38 +1507,47 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>564960</v>
+        <v>564844</v>
       </c>
       <c r="R9" t="n">
-        <v>6443030</v>
+        <v>6443043</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1570,7 +1579,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1580,7 +1589,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1607,7 +1616,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123880241</v>
+        <v>123880057</v>
       </c>
       <c r="B10" t="n">
         <v>98079</v>
@@ -1642,7 +1651,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1656,13 +1665,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>564938</v>
+        <v>564855</v>
       </c>
       <c r="R10" t="n">
-        <v>6443106</v>
+        <v>6443055</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1691,7 +1700,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1701,7 +1710,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1728,10 +1737,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123878490</v>
+        <v>123878450</v>
       </c>
       <c r="B11" t="n">
-        <v>57861</v>
+        <v>57644</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1740,28 +1749,33 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
@@ -1803,7 +1817,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1813,7 +1827,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1840,10 +1854,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123878450</v>
+        <v>123879574</v>
       </c>
       <c r="B12" t="n">
-        <v>57644</v>
+        <v>98079</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1852,31 +1866,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1885,13 +1903,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>564933</v>
+        <v>564879</v>
       </c>
       <c r="R12" t="n">
-        <v>6443065</v>
+        <v>6443023</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1920,7 +1938,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1930,7 +1948,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1957,7 +1975,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123878969</v>
+        <v>123878116</v>
       </c>
       <c r="B13" t="n">
         <v>98079</v>
@@ -1992,7 +2010,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2006,10 +2024,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>564923</v>
+        <v>564947</v>
       </c>
       <c r="R13" t="n">
-        <v>6443028</v>
+        <v>6443069</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -2041,7 +2059,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2051,7 +2069,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2078,7 +2096,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123879729</v>
+        <v>123878216</v>
       </c>
       <c r="B14" t="n">
         <v>98079</v>
@@ -2113,7 +2131,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2127,10 +2145,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>564847</v>
+        <v>564936</v>
       </c>
       <c r="R14" t="n">
-        <v>6443048</v>
+        <v>6443067</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2162,7 +2180,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2172,7 +2190,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2199,7 +2217,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123880057</v>
+        <v>123878885</v>
       </c>
       <c r="B15" t="n">
         <v>98079</v>
@@ -2234,7 +2252,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2248,13 +2266,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>564855</v>
+        <v>564921</v>
       </c>
       <c r="R15" t="n">
-        <v>6443055</v>
+        <v>6443041</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2283,7 +2301,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2293,7 +2311,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2320,7 +2338,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123879574</v>
+        <v>123879729</v>
       </c>
       <c r="B16" t="n">
         <v>98079</v>
@@ -2355,7 +2373,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2369,13 +2387,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>564879</v>
+        <v>564847</v>
       </c>
       <c r="R16" t="n">
-        <v>6443023</v>
+        <v>6443048</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2404,7 +2422,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2414,7 +2432,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2441,10 +2459,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123879049</v>
+        <v>123878490</v>
       </c>
       <c r="B17" t="n">
-        <v>98079</v>
+        <v>57861</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2453,50 +2471,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>564930</v>
+        <v>564933</v>
       </c>
       <c r="R17" t="n">
-        <v>6443013</v>
+        <v>6443065</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2525,7 +2534,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2535,7 +2544,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2562,7 +2571,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123879656</v>
+        <v>123879901</v>
       </c>
       <c r="B18" t="n">
         <v>98079</v>
@@ -2595,29 +2604,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>564864</v>
+        <v>564839</v>
       </c>
       <c r="R18" t="n">
-        <v>6443040</v>
+        <v>6443048</v>
       </c>
       <c r="S18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2683,7 +2683,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123878216</v>
+        <v>123880241</v>
       </c>
       <c r="B19" t="n">
         <v>98079</v>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>564936</v>
+        <v>564938</v>
       </c>
       <c r="R19" t="n">
-        <v>6443067</v>
+        <v>6443106</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2767,7 +2767,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2777,7 +2777,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2804,7 +2804,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123878116</v>
+        <v>123879942</v>
       </c>
       <c r="B20" t="n">
         <v>98079</v>
@@ -2839,7 +2839,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2853,13 +2853,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>564947</v>
+        <v>564852</v>
       </c>
       <c r="R20" t="n">
-        <v>6443069</v>
+        <v>6443050</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2925,7 +2925,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123879901</v>
+        <v>123878969</v>
       </c>
       <c r="B21" t="n">
         <v>98079</v>
@@ -2958,17 +2958,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>564839</v>
+        <v>564923</v>
       </c>
       <c r="R21" t="n">
-        <v>6443048</v>
+        <v>6443028</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -3000,7 +3009,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3010,7 +3019,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3037,10 +3046,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123878885</v>
+        <v>123879278</v>
       </c>
       <c r="B22" t="n">
-        <v>98079</v>
+        <v>105095</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3049,50 +3058,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>564921</v>
+        <v>564960</v>
       </c>
       <c r="R22" t="n">
-        <v>6443041</v>
+        <v>6443030</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3279,7 +3279,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123931443</v>
+        <v>123931662</v>
       </c>
       <c r="B24" t="n">
         <v>98079</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
@@ -3327,10 +3327,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>564864</v>
+        <v>564941</v>
       </c>
       <c r="R24" t="n">
-        <v>6443083</v>
+        <v>6443068</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3362,7 +3362,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3372,7 +3372,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3400,10 +3400,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123932605</v>
+        <v>123931935</v>
       </c>
       <c r="B25" t="n">
-        <v>98079</v>
+        <v>57507</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3412,42 +3412,50 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>St Ved a10555, St Ved a10555, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>564936</v>
+        <v>564955</v>
       </c>
       <c r="R25" t="n">
-        <v>6443071</v>
+        <v>6443078</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3479,7 +3487,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3489,7 +3497,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3516,10 +3524,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123931935</v>
+        <v>123932605</v>
       </c>
       <c r="B26" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3528,50 +3536,42 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>St Ved a10555, St Ved a10555, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>564955</v>
+        <v>564936</v>
       </c>
       <c r="R26" t="n">
-        <v>6443078</v>
+        <v>6443071</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3603,7 +3603,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3613,7 +3613,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3761,7 +3761,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123931662</v>
+        <v>123931443</v>
       </c>
       <c r="B28" t="n">
         <v>98079</v>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
@@ -3809,10 +3809,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>564941</v>
+        <v>564864</v>
       </c>
       <c r="R28" t="n">
-        <v>6443068</v>
+        <v>6443083</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3844,7 +3844,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 10555-2025 artfynd.xlsx
+++ b/artfynd/A 10555-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123879826</v>
+        <v>123878394</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>564844</v>
+        <v>564933</v>
       </c>
       <c r="R2" t="n">
-        <v>6443043</v>
+        <v>6443065</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123879288</v>
+        <v>123878852</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,41 +808,50 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>564960</v>
+        <v>564916</v>
       </c>
       <c r="R3" t="n">
-        <v>6443030</v>
+        <v>6443042</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,7 +917,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123878855</v>
+        <v>123879154</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -941,29 +950,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>564916</v>
+        <v>564947</v>
       </c>
       <c r="R4" t="n">
-        <v>6443042</v>
+        <v>6443012</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1150,10 +1150,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123878327</v>
+        <v>123878450</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1162,35 +1162,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1205,7 +1201,7 @@
         <v>6443065</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1234,7 +1230,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1244,7 +1240,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1271,7 +1267,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123879729</v>
+        <v>123878216</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1306,7 +1302,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1320,10 +1316,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564847</v>
+        <v>564936</v>
       </c>
       <c r="R7" t="n">
-        <v>6443048</v>
+        <v>6443067</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1355,7 +1351,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1365,7 +1361,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1392,10 +1388,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123878490</v>
+        <v>123879278</v>
       </c>
       <c r="B8" t="n">
-        <v>57883</v>
+        <v>105117</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1408,21 +1404,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>221144</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1432,13 +1428,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564933</v>
+        <v>564960</v>
       </c>
       <c r="R8" t="n">
-        <v>6443065</v>
+        <v>6443030</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1467,7 +1463,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1477,7 +1473,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1504,10 +1500,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123879867</v>
+        <v>123880241</v>
       </c>
       <c r="B9" t="n">
-        <v>105117</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1516,38 +1512,47 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>564844</v>
+        <v>564938</v>
       </c>
       <c r="R9" t="n">
-        <v>6443043</v>
+        <v>6443106</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1579,7 +1584,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1589,7 +1594,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1616,7 +1621,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123879656</v>
+        <v>123880057</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1651,7 +1656,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1665,13 +1670,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>564864</v>
+        <v>564855</v>
       </c>
       <c r="R10" t="n">
-        <v>6443040</v>
+        <v>6443055</v>
       </c>
       <c r="S10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1700,7 +1705,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1710,7 +1715,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1737,7 +1742,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123878116</v>
+        <v>123879656</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1772,7 +1777,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1786,13 +1791,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>564947</v>
+        <v>564864</v>
       </c>
       <c r="R11" t="n">
-        <v>6443069</v>
+        <v>6443040</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1821,7 +1826,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1831,7 +1836,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1858,10 +1863,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123880057</v>
+        <v>123879288</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1870,50 +1875,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>564855</v>
+        <v>564960</v>
       </c>
       <c r="R12" t="n">
-        <v>6443055</v>
+        <v>6443030</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1942,7 +1938,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1952,7 +1948,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2100,10 +2096,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123879942</v>
+        <v>123879867</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>105117</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2112,50 +2108,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>564852</v>
+        <v>564844</v>
       </c>
       <c r="R14" t="n">
-        <v>6443050</v>
+        <v>6443043</v>
       </c>
       <c r="S14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2184,7 +2171,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2194,7 +2181,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2221,7 +2208,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123878216</v>
+        <v>123879574</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2256,7 +2243,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2270,13 +2257,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>564936</v>
+        <v>564879</v>
       </c>
       <c r="R15" t="n">
-        <v>6443067</v>
+        <v>6443023</v>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2305,7 +2292,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2315,7 +2302,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2342,7 +2329,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123880241</v>
+        <v>123879901</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2375,26 +2362,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>564938</v>
+        <v>564839</v>
       </c>
       <c r="R16" t="n">
-        <v>6443106</v>
+        <v>6443048</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2426,7 +2404,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2436,7 +2414,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2463,10 +2441,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123879278</v>
+        <v>123878885</v>
       </c>
       <c r="B17" t="n">
-        <v>105117</v>
+        <v>98101</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2475,41 +2453,50 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>564960</v>
+        <v>564921</v>
       </c>
       <c r="R17" t="n">
-        <v>6443030</v>
+        <v>6443041</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2538,7 +2525,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2548,7 +2535,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2575,7 +2562,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123879574</v>
+        <v>123879942</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2610,7 +2597,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2624,13 +2611,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>564879</v>
+        <v>564852</v>
       </c>
       <c r="R18" t="n">
-        <v>6443023</v>
+        <v>6443050</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2659,7 +2646,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2669,7 +2656,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2696,7 +2683,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123878885</v>
+        <v>123878116</v>
       </c>
       <c r="B19" t="n">
         <v>98101</v>
@@ -2731,7 +2718,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2745,13 +2732,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>564921</v>
+        <v>564947</v>
       </c>
       <c r="R19" t="n">
-        <v>6443041</v>
+        <v>6443069</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2780,7 +2767,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2790,7 +2777,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2817,10 +2804,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123878450</v>
+        <v>123879729</v>
       </c>
       <c r="B20" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2829,31 +2816,35 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2862,13 +2853,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>564933</v>
+        <v>564847</v>
       </c>
       <c r="R20" t="n">
-        <v>6443065</v>
+        <v>6443048</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2897,7 +2888,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2907,7 +2898,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2934,10 +2925,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123879154</v>
+        <v>123878490</v>
       </c>
       <c r="B21" t="n">
-        <v>98101</v>
+        <v>57883</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2946,25 +2937,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2974,13 +2965,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>564947</v>
+        <v>564933</v>
       </c>
       <c r="R21" t="n">
-        <v>6443012</v>
+        <v>6443065</v>
       </c>
       <c r="S21" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3009,7 +3000,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3019,7 +3010,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3046,7 +3037,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123879901</v>
+        <v>123879826</v>
       </c>
       <c r="B22" t="n">
         <v>98101</v>
@@ -3079,17 +3070,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>564839</v>
+        <v>564844</v>
       </c>
       <c r="R22" t="n">
-        <v>6443048</v>
+        <v>6443043</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -3158,7 +3158,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123931335</v>
+        <v>123931662</v>
       </c>
       <c r="B23" t="n">
         <v>98101</v>
@@ -3193,7 +3193,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
@@ -3206,10 +3206,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>564906</v>
+        <v>564941</v>
       </c>
       <c r="R23" t="n">
-        <v>6443033</v>
+        <v>6443068</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3279,10 +3279,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123932083</v>
+        <v>123931335</v>
       </c>
       <c r="B24" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3291,50 +3291,49 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>St Ved a10555, St Ved a10555, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>564954</v>
+        <v>564906</v>
       </c>
       <c r="R24" t="n">
-        <v>6443052</v>
+        <v>6443033</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3363,7 +3362,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3373,7 +3372,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3382,6 +3381,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3400,10 +3400,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123931935</v>
+        <v>123931443</v>
       </c>
       <c r="B25" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3412,39 +3412,35 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3452,10 +3448,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>564955</v>
+        <v>564864</v>
       </c>
       <c r="R25" t="n">
-        <v>6443078</v>
+        <v>6443083</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3487,7 +3483,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3497,7 +3493,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3506,6 +3502,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3524,7 +3521,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123931662</v>
+        <v>123932605</v>
       </c>
       <c r="B26" t="n">
         <v>98101</v>
@@ -3559,23 +3556,19 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>St Ved a10555, St Ved a10555, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>564941</v>
+        <v>564936</v>
       </c>
       <c r="R26" t="n">
-        <v>6443068</v>
+        <v>6443071</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3607,7 +3600,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3617,7 +3610,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3626,7 +3619,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3645,10 +3637,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123931443</v>
+        <v>123931935</v>
       </c>
       <c r="B27" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3657,35 +3649,39 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3693,10 +3689,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>564864</v>
+        <v>564955</v>
       </c>
       <c r="R27" t="n">
-        <v>6443083</v>
+        <v>6443078</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3728,7 +3724,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3738,7 +3734,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3747,7 +3743,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3766,10 +3761,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123932605</v>
+        <v>123932083</v>
       </c>
       <c r="B28" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3778,30 +3773,35 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3810,13 +3810,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>564936</v>
+        <v>564954</v>
       </c>
       <c r="R28" t="n">
-        <v>6443071</v>
+        <v>6443052</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3855,7 +3855,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 10555-2025 artfynd.xlsx
+++ b/artfynd/A 10555-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123878394</v>
+        <v>123879729</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>564933</v>
+        <v>564847</v>
       </c>
       <c r="R2" t="n">
-        <v>6443065</v>
+        <v>6443048</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,7 +796,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123878852</v>
+        <v>123878777</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -917,7 +917,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123879154</v>
+        <v>123878216</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -950,17 +950,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>564947</v>
+        <v>564936</v>
       </c>
       <c r="R4" t="n">
-        <v>6443012</v>
+        <v>6443067</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -992,7 +1001,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +1011,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,10 +1038,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123878969</v>
+        <v>123879278</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>105117</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,47 +1050,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>564923</v>
+        <v>564960</v>
       </c>
       <c r="R5" t="n">
-        <v>6443028</v>
+        <v>6443030</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1150,10 +1150,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123878450</v>
+        <v>123878885</v>
       </c>
       <c r="B6" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1162,31 +1162,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1195,13 +1199,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>564933</v>
+        <v>564921</v>
       </c>
       <c r="R6" t="n">
-        <v>6443065</v>
+        <v>6443041</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1230,7 +1234,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1240,7 +1244,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1267,7 +1271,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123878216</v>
+        <v>123878394</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1316,10 +1320,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564936</v>
+        <v>564933</v>
       </c>
       <c r="R7" t="n">
-        <v>6443067</v>
+        <v>6443065</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1351,7 +1355,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1361,7 +1365,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1388,10 +1392,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123879278</v>
+        <v>123879574</v>
       </c>
       <c r="B8" t="n">
-        <v>105117</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1400,41 +1404,50 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564960</v>
+        <v>564879</v>
       </c>
       <c r="R8" t="n">
-        <v>6443030</v>
+        <v>6443023</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1463,7 +1476,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1473,7 +1486,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1500,7 +1513,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123880241</v>
+        <v>123879130</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1533,26 +1546,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>564938</v>
+        <v>564947</v>
       </c>
       <c r="R9" t="n">
-        <v>6443106</v>
+        <v>6443012</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1584,7 +1588,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1594,7 +1598,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1621,7 +1625,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123880057</v>
+        <v>123879826</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1670,13 +1674,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>564855</v>
+        <v>564844</v>
       </c>
       <c r="R10" t="n">
-        <v>6443055</v>
+        <v>6443043</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1705,7 +1709,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1715,7 +1719,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1742,7 +1746,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123879656</v>
+        <v>123879049</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1777,7 +1781,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1791,13 +1795,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>564864</v>
+        <v>564930</v>
       </c>
       <c r="R11" t="n">
-        <v>6443040</v>
+        <v>6443013</v>
       </c>
       <c r="S11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1826,7 +1830,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1836,7 +1840,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1863,10 +1867,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123879288</v>
+        <v>123880241</v>
       </c>
       <c r="B12" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1875,41 +1879,50 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>564960</v>
+        <v>564938</v>
       </c>
       <c r="R12" t="n">
-        <v>6443030</v>
+        <v>6443106</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1938,7 +1951,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1948,7 +1961,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1975,7 +1988,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123879049</v>
+        <v>123879901</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -2008,26 +2021,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>564930</v>
+        <v>564839</v>
       </c>
       <c r="R13" t="n">
-        <v>6443013</v>
+        <v>6443048</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -2059,7 +2063,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2069,7 +2073,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2096,10 +2100,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123879867</v>
+        <v>123878490</v>
       </c>
       <c r="B14" t="n">
-        <v>105117</v>
+        <v>57883</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2112,21 +2116,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221144</v>
+        <v>103015</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2136,13 +2140,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>564844</v>
+        <v>564933</v>
       </c>
       <c r="R14" t="n">
-        <v>6443043</v>
+        <v>6443065</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2171,7 +2175,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2181,7 +2185,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2208,7 +2212,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123879574</v>
+        <v>123878969</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2243,7 +2247,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2257,13 +2261,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>564879</v>
+        <v>564923</v>
       </c>
       <c r="R15" t="n">
-        <v>6443023</v>
+        <v>6443028</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2292,7 +2296,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2302,7 +2306,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2329,7 +2333,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123879901</v>
+        <v>123880057</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2362,20 +2366,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>564839</v>
+        <v>564855</v>
       </c>
       <c r="R16" t="n">
-        <v>6443048</v>
+        <v>6443055</v>
       </c>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2404,7 +2417,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2414,7 +2427,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2441,7 +2454,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123878885</v>
+        <v>123879942</v>
       </c>
       <c r="B17" t="n">
         <v>98101</v>
@@ -2476,7 +2489,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2490,13 +2503,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>564921</v>
+        <v>564852</v>
       </c>
       <c r="R17" t="n">
-        <v>6443041</v>
+        <v>6443050</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2525,7 +2538,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2535,7 +2548,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2562,10 +2575,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123879942</v>
+        <v>123878450</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2574,35 +2587,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2611,13 +2620,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>564852</v>
+        <v>564933</v>
       </c>
       <c r="R18" t="n">
-        <v>6443050</v>
+        <v>6443065</v>
       </c>
       <c r="S18" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2646,7 +2655,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2656,7 +2665,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2683,7 +2692,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123878116</v>
+        <v>123879656</v>
       </c>
       <c r="B19" t="n">
         <v>98101</v>
@@ -2718,7 +2727,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2732,13 +2741,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>564947</v>
+        <v>564864</v>
       </c>
       <c r="R19" t="n">
-        <v>6443069</v>
+        <v>6443040</v>
       </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2767,7 +2776,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2777,7 +2786,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2804,10 +2813,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123879729</v>
+        <v>123879867</v>
       </c>
       <c r="B20" t="n">
-        <v>98101</v>
+        <v>105117</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2816,47 +2825,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>564847</v>
+        <v>564844</v>
       </c>
       <c r="R20" t="n">
-        <v>6443048</v>
+        <v>6443043</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2888,7 +2888,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2925,10 +2925,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123878490</v>
+        <v>123879288</v>
       </c>
       <c r="B21" t="n">
-        <v>57883</v>
+        <v>57529</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2937,20 +2937,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>564933</v>
+        <v>564960</v>
       </c>
       <c r="R21" t="n">
-        <v>6443065</v>
+        <v>6443030</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3010,7 +3010,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3037,7 +3037,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123879826</v>
+        <v>123878116</v>
       </c>
       <c r="B22" t="n">
         <v>98101</v>
@@ -3072,7 +3072,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3086,10 +3086,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>564844</v>
+        <v>564947</v>
       </c>
       <c r="R22" t="n">
-        <v>6443043</v>
+        <v>6443069</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3158,10 +3158,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123931662</v>
+        <v>123932083</v>
       </c>
       <c r="B23" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3170,49 +3170,50 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>St Ved a10555, St Ved a10555, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>564941</v>
+        <v>564954</v>
       </c>
       <c r="R23" t="n">
-        <v>6443068</v>
+        <v>6443052</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3241,7 +3242,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3251,7 +3252,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3260,7 +3261,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3279,7 +3279,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123931335</v>
+        <v>123932605</v>
       </c>
       <c r="B24" t="n">
         <v>98101</v>
@@ -3314,23 +3314,19 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>St Ved a10555, St Ved a10555, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>564906</v>
+        <v>564936</v>
       </c>
       <c r="R24" t="n">
-        <v>6443033</v>
+        <v>6443071</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3362,7 +3358,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3372,7 +3368,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3381,7 +3377,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3521,7 +3516,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123932605</v>
+        <v>123931335</v>
       </c>
       <c r="B26" t="n">
         <v>98101</v>
@@ -3556,19 +3551,23 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>St Ved a10555, St Ved a10555, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>564936</v>
+        <v>564906</v>
       </c>
       <c r="R26" t="n">
-        <v>6443071</v>
+        <v>6443033</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3600,7 +3599,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3610,7 +3609,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3619,6 +3618,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3761,10 +3761,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123932083</v>
+        <v>123931662</v>
       </c>
       <c r="B28" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3773,50 +3773,49 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>St Ved a10555, St Ved a10555, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>564954</v>
+        <v>564941</v>
       </c>
       <c r="R28" t="n">
-        <v>6443052</v>
+        <v>6443068</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3845,7 +3844,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3855,7 +3854,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3864,6 +3863,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 10555-2025 artfynd.xlsx
+++ b/artfynd/A 10555-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123879729</v>
+        <v>123878394</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>564847</v>
+        <v>564933</v>
       </c>
       <c r="R2" t="n">
-        <v>6443048</v>
+        <v>6443065</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,7 +796,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123878777</v>
+        <v>123879826</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -831,7 +831,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -845,13 +845,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>564916</v>
+        <v>564844</v>
       </c>
       <c r="R3" t="n">
-        <v>6443042</v>
+        <v>6443043</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,7 +917,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123878216</v>
+        <v>123879729</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -952,7 +952,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -966,10 +966,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>564936</v>
+        <v>564847</v>
       </c>
       <c r="R4" t="n">
-        <v>6443067</v>
+        <v>6443048</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,10 +1038,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123879278</v>
+        <v>123878969</v>
       </c>
       <c r="B5" t="n">
-        <v>105117</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1050,38 +1050,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>564960</v>
+        <v>564923</v>
       </c>
       <c r="R5" t="n">
-        <v>6443030</v>
+        <v>6443028</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1113,7 +1122,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1123,7 +1132,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1150,7 +1159,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123878885</v>
+        <v>123878804</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1199,10 +1208,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>564921</v>
+        <v>564916</v>
       </c>
       <c r="R6" t="n">
-        <v>6443041</v>
+        <v>6443042</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1234,7 +1243,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1244,7 +1253,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1271,7 +1280,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123878394</v>
+        <v>123879574</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1306,7 +1315,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1320,13 +1329,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564933</v>
+        <v>564879</v>
       </c>
       <c r="R7" t="n">
-        <v>6443065</v>
+        <v>6443023</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1355,7 +1364,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1365,7 +1374,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1392,10 +1401,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123879574</v>
+        <v>123879278</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>105117</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1404,50 +1413,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564879</v>
+        <v>564960</v>
       </c>
       <c r="R8" t="n">
-        <v>6443023</v>
+        <v>6443030</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1625,10 +1625,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123879826</v>
+        <v>123879288</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1637,50 +1637,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>564844</v>
+        <v>564960</v>
       </c>
       <c r="R10" t="n">
-        <v>6443043</v>
+        <v>6443030</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1709,7 +1700,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1719,7 +1710,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1746,7 +1737,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123879049</v>
+        <v>123878216</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1781,7 +1772,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1795,10 +1786,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>564930</v>
+        <v>564936</v>
       </c>
       <c r="R11" t="n">
-        <v>6443013</v>
+        <v>6443067</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1830,7 +1821,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1840,7 +1831,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1867,10 +1858,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123880241</v>
+        <v>123878490</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>57883</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1879,50 +1870,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>564938</v>
+        <v>564933</v>
       </c>
       <c r="R12" t="n">
-        <v>6443106</v>
+        <v>6443065</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1951,7 +1933,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1961,7 +1943,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1988,7 +1970,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123879901</v>
+        <v>123879942</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -2021,20 +2003,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>564839</v>
+        <v>564852</v>
       </c>
       <c r="R13" t="n">
-        <v>6443048</v>
+        <v>6443050</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2063,7 +2054,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2073,7 +2064,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2100,10 +2091,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123878490</v>
+        <v>123878116</v>
       </c>
       <c r="B14" t="n">
-        <v>57883</v>
+        <v>98101</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2112,41 +2103,50 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>564933</v>
+        <v>564947</v>
       </c>
       <c r="R14" t="n">
-        <v>6443065</v>
+        <v>6443069</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2185,7 +2185,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2212,7 +2212,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123878969</v>
+        <v>123879656</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2247,7 +2247,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2261,13 +2261,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>564923</v>
+        <v>564864</v>
       </c>
       <c r="R15" t="n">
-        <v>6443028</v>
+        <v>6443040</v>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2333,10 +2333,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123880057</v>
+        <v>123879867</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
+        <v>105117</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2345,50 +2345,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>564855</v>
+        <v>564844</v>
       </c>
       <c r="R16" t="n">
-        <v>6443055</v>
+        <v>6443043</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2417,7 +2408,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2427,7 +2418,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2454,7 +2445,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123879942</v>
+        <v>123879901</v>
       </c>
       <c r="B17" t="n">
         <v>98101</v>
@@ -2487,29 +2478,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>564852</v>
+        <v>564839</v>
       </c>
       <c r="R17" t="n">
-        <v>6443050</v>
+        <v>6443048</v>
       </c>
       <c r="S17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2538,7 +2520,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2548,7 +2530,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2575,10 +2557,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123878450</v>
+        <v>123880057</v>
       </c>
       <c r="B18" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2587,31 +2569,35 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2620,13 +2606,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>564933</v>
+        <v>564855</v>
       </c>
       <c r="R18" t="n">
-        <v>6443065</v>
+        <v>6443055</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2655,7 +2641,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2665,7 +2651,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2692,7 +2678,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123879656</v>
+        <v>123879049</v>
       </c>
       <c r="B19" t="n">
         <v>98101</v>
@@ -2727,7 +2713,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2741,13 +2727,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>564864</v>
+        <v>564930</v>
       </c>
       <c r="R19" t="n">
-        <v>6443040</v>
+        <v>6443013</v>
       </c>
       <c r="S19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2776,7 +2762,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2786,7 +2772,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2813,10 +2799,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123879867</v>
+        <v>123878885</v>
       </c>
       <c r="B20" t="n">
-        <v>105117</v>
+        <v>98101</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2825,41 +2811,50 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>564844</v>
+        <v>564921</v>
       </c>
       <c r="R20" t="n">
-        <v>6443043</v>
+        <v>6443041</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2888,7 +2883,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2898,7 +2893,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2925,10 +2920,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123879288</v>
+        <v>123878450</v>
       </c>
       <c r="B21" t="n">
-        <v>57529</v>
+        <v>57666</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2941,34 +2936,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>564960</v>
+        <v>564933</v>
       </c>
       <c r="R21" t="n">
-        <v>6443030</v>
+        <v>6443065</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3010,7 +3010,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3037,7 +3037,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123878116</v>
+        <v>123880241</v>
       </c>
       <c r="B22" t="n">
         <v>98101</v>
@@ -3072,7 +3072,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3086,10 +3086,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>564947</v>
+        <v>564938</v>
       </c>
       <c r="R22" t="n">
-        <v>6443069</v>
+        <v>6443106</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3158,10 +3158,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123932083</v>
+        <v>123931335</v>
       </c>
       <c r="B23" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3170,50 +3170,49 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>St Ved a10555, St Ved a10555, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>564954</v>
+        <v>564906</v>
       </c>
       <c r="R23" t="n">
-        <v>6443052</v>
+        <v>6443033</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3242,7 +3241,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3252,7 +3251,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3261,6 +3260,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3279,7 +3279,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123932605</v>
+        <v>123931662</v>
       </c>
       <c r="B24" t="n">
         <v>98101</v>
@@ -3314,19 +3314,23 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>St Ved a10555, St Ved a10555, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>564936</v>
+        <v>564941</v>
       </c>
       <c r="R24" t="n">
-        <v>6443071</v>
+        <v>6443068</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3358,7 +3362,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3368,7 +3372,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3377,6 +3381,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3395,10 +3400,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123931443</v>
+        <v>123931935</v>
       </c>
       <c r="B25" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3407,35 +3412,39 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3443,10 +3452,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>564864</v>
+        <v>564955</v>
       </c>
       <c r="R25" t="n">
-        <v>6443083</v>
+        <v>6443078</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3478,7 +3487,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3488,7 +3497,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3497,7 +3506,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3516,7 +3524,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123931335</v>
+        <v>123931443</v>
       </c>
       <c r="B26" t="n">
         <v>98101</v>
@@ -3564,10 +3572,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>564906</v>
+        <v>564864</v>
       </c>
       <c r="R26" t="n">
-        <v>6443033</v>
+        <v>6443083</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3599,7 +3607,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3609,7 +3617,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3637,10 +3645,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123931935</v>
+        <v>123932605</v>
       </c>
       <c r="B27" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3649,50 +3657,42 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>St Ved a10555, St Ved a10555, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>564955</v>
+        <v>564936</v>
       </c>
       <c r="R27" t="n">
-        <v>6443078</v>
+        <v>6443071</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3724,7 +3724,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3734,7 +3734,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3761,10 +3761,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123931662</v>
+        <v>123932083</v>
       </c>
       <c r="B28" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3773,49 +3773,50 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>St Ved a10555, St Ved a10555, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>564941</v>
+        <v>564954</v>
       </c>
       <c r="R28" t="n">
-        <v>6443068</v>
+        <v>6443052</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3844,7 +3845,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3854,7 +3855,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3863,7 +3864,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 10555-2025 artfynd.xlsx
+++ b/artfynd/A 10555-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123878394</v>
+        <v>123880241</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>564933</v>
+        <v>564938</v>
       </c>
       <c r="R2" t="n">
-        <v>6443065</v>
+        <v>6443106</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,7 +796,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123879826</v>
+        <v>123878780</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -831,7 +831,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -845,13 +845,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>564844</v>
+        <v>564916</v>
       </c>
       <c r="R3" t="n">
-        <v>6443043</v>
+        <v>6443042</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,7 +917,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123879729</v>
+        <v>123880057</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -952,7 +952,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -966,13 +966,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>564847</v>
+        <v>564855</v>
       </c>
       <c r="R4" t="n">
-        <v>6443048</v>
+        <v>6443055</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,7 +1038,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123878969</v>
+        <v>123879154</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1071,26 +1071,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>564923</v>
+        <v>564947</v>
       </c>
       <c r="R5" t="n">
-        <v>6443028</v>
+        <v>6443012</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1122,7 +1113,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1132,7 +1123,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,7 +1150,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123878804</v>
+        <v>123878371</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1194,7 +1185,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1208,13 +1199,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>564916</v>
+        <v>564933</v>
       </c>
       <c r="R6" t="n">
-        <v>6443042</v>
+        <v>6443065</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1243,7 +1234,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1253,7 +1244,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1280,10 +1271,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123879574</v>
+        <v>123879867</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>105117</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1292,50 +1283,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564879</v>
+        <v>564844</v>
       </c>
       <c r="R7" t="n">
-        <v>6443023</v>
+        <v>6443043</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1364,7 +1346,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1374,7 +1356,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1401,10 +1383,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123879278</v>
+        <v>123879826</v>
       </c>
       <c r="B8" t="n">
-        <v>105117</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1413,38 +1395,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564960</v>
+        <v>564844</v>
       </c>
       <c r="R8" t="n">
-        <v>6443030</v>
+        <v>6443043</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1476,7 +1467,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1486,7 +1477,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1513,7 +1504,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123879130</v>
+        <v>123878216</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1546,17 +1537,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>564947</v>
+        <v>564936</v>
       </c>
       <c r="R9" t="n">
-        <v>6443012</v>
+        <v>6443067</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1625,10 +1625,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123879288</v>
+        <v>123878450</v>
       </c>
       <c r="B10" t="n">
-        <v>57529</v>
+        <v>57666</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1641,34 +1641,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>564960</v>
+        <v>564933</v>
       </c>
       <c r="R10" t="n">
-        <v>6443030</v>
+        <v>6443065</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1700,7 +1705,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1710,7 +1715,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1737,10 +1742,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123878216</v>
+        <v>123879288</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1749,50 +1754,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>564936</v>
+        <v>564960</v>
       </c>
       <c r="R11" t="n">
-        <v>6443067</v>
+        <v>6443030</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1821,7 +1817,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1831,7 +1827,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1858,10 +1854,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123878490</v>
+        <v>123878116</v>
       </c>
       <c r="B12" t="n">
-        <v>57883</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1870,41 +1866,50 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>564933</v>
+        <v>564947</v>
       </c>
       <c r="R12" t="n">
-        <v>6443065</v>
+        <v>6443069</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1933,7 +1938,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1943,7 +1948,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1970,7 +1975,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123879942</v>
+        <v>123878885</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -2005,7 +2010,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2019,13 +2024,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>564852</v>
+        <v>564921</v>
       </c>
       <c r="R13" t="n">
-        <v>6443050</v>
+        <v>6443041</v>
       </c>
       <c r="S13" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2054,7 +2059,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2064,7 +2069,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2091,10 +2096,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123878116</v>
+        <v>123878490</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>57883</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2103,50 +2108,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>564947</v>
+        <v>564933</v>
       </c>
       <c r="R14" t="n">
-        <v>6443069</v>
+        <v>6443065</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2175,7 +2171,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2185,7 +2181,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2333,10 +2329,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123879867</v>
+        <v>123879049</v>
       </c>
       <c r="B16" t="n">
-        <v>105117</v>
+        <v>98101</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2345,38 +2341,47 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>564844</v>
+        <v>564930</v>
       </c>
       <c r="R16" t="n">
-        <v>6443043</v>
+        <v>6443013</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2408,7 +2413,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2418,7 +2423,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2445,7 +2450,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123879901</v>
+        <v>123878969</v>
       </c>
       <c r="B17" t="n">
         <v>98101</v>
@@ -2478,17 +2483,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>564839</v>
+        <v>564923</v>
       </c>
       <c r="R17" t="n">
-        <v>6443048</v>
+        <v>6443028</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2520,7 +2534,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2530,7 +2544,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2557,10 +2571,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123880057</v>
+        <v>123879278</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
+        <v>105117</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2569,50 +2583,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>564855</v>
+        <v>564960</v>
       </c>
       <c r="R18" t="n">
-        <v>6443055</v>
+        <v>6443030</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2641,7 +2646,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2651,7 +2656,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2678,7 +2683,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123879049</v>
+        <v>123879942</v>
       </c>
       <c r="B19" t="n">
         <v>98101</v>
@@ -2713,7 +2718,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2727,13 +2732,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>564930</v>
+        <v>564852</v>
       </c>
       <c r="R19" t="n">
-        <v>6443013</v>
+        <v>6443050</v>
       </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2762,7 +2767,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2772,7 +2777,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2799,7 +2804,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123878885</v>
+        <v>123879729</v>
       </c>
       <c r="B20" t="n">
         <v>98101</v>
@@ -2834,7 +2839,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2848,13 +2853,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>564921</v>
+        <v>564847</v>
       </c>
       <c r="R20" t="n">
-        <v>6443041</v>
+        <v>6443048</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2883,7 +2888,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2893,7 +2898,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2920,10 +2925,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123878450</v>
+        <v>123879901</v>
       </c>
       <c r="B21" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2932,46 +2937,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hortkärr, Hortkärr, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>564933</v>
+        <v>564839</v>
       </c>
       <c r="R21" t="n">
-        <v>6443065</v>
+        <v>6443048</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3010,7 +3010,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3037,7 +3037,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123880241</v>
+        <v>123879574</v>
       </c>
       <c r="B22" t="n">
         <v>98101</v>
@@ -3072,7 +3072,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3086,13 +3086,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>564938</v>
+        <v>564879</v>
       </c>
       <c r="R22" t="n">
-        <v>6443106</v>
+        <v>6443023</v>
       </c>
       <c r="S22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3279,10 +3279,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123931662</v>
+        <v>123931935</v>
       </c>
       <c r="B24" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3291,35 +3291,39 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3327,10 +3331,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>564941</v>
+        <v>564955</v>
       </c>
       <c r="R24" t="n">
-        <v>6443068</v>
+        <v>6443078</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3362,7 +3366,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3372,7 +3376,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3381,7 +3385,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3400,10 +3403,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123931935</v>
+        <v>123932605</v>
       </c>
       <c r="B25" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3412,50 +3415,42 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>St Ved a10555, St Ved a10555, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>564955</v>
+        <v>564936</v>
       </c>
       <c r="R25" t="n">
-        <v>6443078</v>
+        <v>6443071</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3487,7 +3482,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3497,7 +3492,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3645,10 +3640,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123932605</v>
+        <v>123932083</v>
       </c>
       <c r="B27" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3657,30 +3652,35 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3689,13 +3689,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>564936</v>
+        <v>564954</v>
       </c>
       <c r="R27" t="n">
-        <v>6443071</v>
+        <v>6443052</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3734,7 +3734,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3761,10 +3761,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123932083</v>
+        <v>123931662</v>
       </c>
       <c r="B28" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3773,50 +3773,49 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>St Ved a10555, St Ved a10555, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>564954</v>
+        <v>564941</v>
       </c>
       <c r="R28" t="n">
-        <v>6443052</v>
+        <v>6443068</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3845,7 +3844,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3855,7 +3854,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3864,6 +3863,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 10555-2025 artfynd.xlsx
+++ b/artfynd/A 10555-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3880,6 +3880,745 @@
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>128701851</v>
+      </c>
+      <c r="B29" t="n">
+        <v>92161</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Hortkärr, Sm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>564892</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6443027</v>
+      </c>
+      <c r="S29" t="n">
+        <v>17</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Gärdserum</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>128701858</v>
+      </c>
+      <c r="B30" t="n">
+        <v>98585</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Hortkärr, Sm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>564892</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6443027</v>
+      </c>
+      <c r="S30" t="n">
+        <v>17</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Gärdserum</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>128701786</v>
+      </c>
+      <c r="B31" t="n">
+        <v>74985</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6428</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Rostfläck</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Arthonia vinosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Hortkärr, Sm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>564864</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6443091</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Gärdserum</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>128701844</v>
+      </c>
+      <c r="B32" t="n">
+        <v>58059</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Hortkärr, Sm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>564835</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6443037</v>
+      </c>
+      <c r="S32" t="n">
+        <v>19</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Gärdserum</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>128701846</v>
+      </c>
+      <c r="B33" t="n">
+        <v>58366</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Hortkärr, Sm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>564835</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6443037</v>
+      </c>
+      <c r="S33" t="n">
+        <v>19</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Gärdserum</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>128700860</v>
+      </c>
+      <c r="B34" t="n">
+        <v>91237</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Hortkärr, Sm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>564931</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6443037</v>
+      </c>
+      <c r="S34" t="n">
+        <v>18</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Gärdserum</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 10555-2025 artfynd.xlsx
+++ b/artfynd/A 10555-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4502,123 +4502,6 @@
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>128700860</v>
-      </c>
-      <c r="B34" t="n">
-        <v>91237</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>3215</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Rödgul trumpetsvamp</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Craterellus lutescens</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>Hortkärr, Sm</t>
-        </is>
-      </c>
-      <c r="Q34" t="n">
-        <v>564931</v>
-      </c>
-      <c r="R34" t="n">
-        <v>6443037</v>
-      </c>
-      <c r="S34" t="n">
-        <v>18</v>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>Åtvidaberg</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>Gärdserum</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>14:40</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>14:40</t>
-        </is>
-      </c>
-      <c r="AD34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT34" t="inlineStr"/>
-      <c r="AW34" t="inlineStr">
-        <is>
-          <t>William Rosén</t>
-        </is>
-      </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>William Rosén</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 10555-2025 artfynd.xlsx
+++ b/artfynd/A 10555-2025 artfynd.xlsx
@@ -3885,7 +3885,7 @@
         <v>128701851</v>
       </c>
       <c r="B29" t="n">
-        <v>92161</v>
+        <v>92163</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         <v>128701858</v>
       </c>
       <c r="B30" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>128701786</v>
       </c>
       <c r="B31" t="n">
-        <v>74985</v>
+        <v>74987</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 10555-2025 artfynd.xlsx
+++ b/artfynd/A 10555-2025 artfynd.xlsx
@@ -4002,7 +4002,7 @@
         <v>128701858</v>
       </c>
       <c r="B30" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 10555-2025 artfynd.xlsx
+++ b/artfynd/A 10555-2025 artfynd.xlsx
@@ -3885,7 +3885,7 @@
         <v>128701851</v>
       </c>
       <c r="B29" t="n">
-        <v>92163</v>
+        <v>92164</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         <v>128701858</v>
       </c>
       <c r="B30" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 10555-2025 artfynd.xlsx
+++ b/artfynd/A 10555-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3882,43 +3882,52 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128701851</v>
+        <v>128701858</v>
       </c>
       <c r="B29" t="n">
-        <v>92164</v>
+        <v>98619</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3962,7 +3971,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3972,7 +3981,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3999,52 +4008,43 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128701858</v>
+        <v>128701786</v>
       </c>
       <c r="B30" t="n">
-        <v>98592</v>
+        <v>75014</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6428</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4053,13 +4053,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>564892</v>
+        <v>564864</v>
       </c>
       <c r="R30" t="n">
-        <v>6443027</v>
+        <v>6443091</v>
       </c>
       <c r="S30" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4098,7 +4098,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4109,6 +4109,26 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Betula pubescens</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4125,10 +4145,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128701786</v>
+        <v>128701844</v>
       </c>
       <c r="B31" t="n">
-        <v>74987</v>
+        <v>58086</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4136,32 +4156,36 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6428</v>
+        <v>103015</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Leight.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4170,13 +4194,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>564864</v>
+        <v>564835</v>
       </c>
       <c r="R31" t="n">
-        <v>6443091</v>
+        <v>6443037</v>
       </c>
       <c r="S31" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4205,7 +4229,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4215,7 +4239,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4226,26 +4250,6 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Betula pubescens</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4262,10 +4266,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128701844</v>
+        <v>128701846</v>
       </c>
       <c r="B32" t="n">
-        <v>58059</v>
+        <v>58393</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4273,16 +4277,16 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -4292,7 +4296,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -4302,7 +4306,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>passiv ljudinspelning</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4380,127 +4384,6 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>128701846</v>
-      </c>
-      <c r="B33" t="n">
-        <v>58366</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>103044</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Grönsiska</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Spinus spinus</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>Hortkärr, Sm</t>
-        </is>
-      </c>
-      <c r="Q33" t="n">
-        <v>564835</v>
-      </c>
-      <c r="R33" t="n">
-        <v>6443037</v>
-      </c>
-      <c r="S33" t="n">
-        <v>19</v>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>Åtvidaberg</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>Gärdserum</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>14:12</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>14:12</t>
-        </is>
-      </c>
-      <c r="AD33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT33" t="inlineStr"/>
-      <c r="AW33" t="inlineStr">
-        <is>
-          <t>William Rosén</t>
-        </is>
-      </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>William Rosén</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 10555-2025 artfynd.xlsx
+++ b/artfynd/A 10555-2025 artfynd.xlsx
@@ -3885,7 +3885,7 @@
         <v>128701858</v>
       </c>
       <c r="B29" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>128701786</v>
       </c>
       <c r="B30" t="n">
-        <v>75014</v>
+        <v>75015</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 10555-2025 artfynd.xlsx
+++ b/artfynd/A 10555-2025 artfynd.xlsx
@@ -3885,7 +3885,7 @@
         <v>128701858</v>
       </c>
       <c r="B29" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 10555-2025 artfynd.xlsx
+++ b/artfynd/A 10555-2025 artfynd.xlsx
@@ -3885,7 +3885,7 @@
         <v>128701858</v>
       </c>
       <c r="B29" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>128701786</v>
       </c>
       <c r="B30" t="n">
-        <v>75015</v>
+        <v>75019</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>128701844</v>
       </c>
       <c r="B31" t="n">
-        <v>58086</v>
+        <v>58090</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>128701846</v>
       </c>
       <c r="B32" t="n">
-        <v>58393</v>
+        <v>58397</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 10555-2025 artfynd.xlsx
+++ b/artfynd/A 10555-2025 artfynd.xlsx
@@ -3885,7 +3885,7 @@
         <v>128701858</v>
       </c>
       <c r="B29" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>128701786</v>
       </c>
       <c r="B30" t="n">
-        <v>75019</v>
+        <v>75022</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>128701844</v>
       </c>
       <c r="B31" t="n">
-        <v>58090</v>
+        <v>58093</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>128701846</v>
       </c>
       <c r="B32" t="n">
-        <v>58397</v>
+        <v>58400</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 10555-2025 artfynd.xlsx
+++ b/artfynd/A 10555-2025 artfynd.xlsx
@@ -3885,7 +3885,7 @@
         <v>128701858</v>
       </c>
       <c r="B29" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>128701786</v>
       </c>
       <c r="B30" t="n">
-        <v>75022</v>
+        <v>75027</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 10555-2025 artfynd.xlsx
+++ b/artfynd/A 10555-2025 artfynd.xlsx
@@ -3885,7 +3885,7 @@
         <v>128701858</v>
       </c>
       <c r="B29" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 10555-2025 artfynd.xlsx
+++ b/artfynd/A 10555-2025 artfynd.xlsx
@@ -3885,7 +3885,7 @@
         <v>128701858</v>
       </c>
       <c r="B29" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 10555-2025 artfynd.xlsx
+++ b/artfynd/A 10555-2025 artfynd.xlsx
@@ -3885,7 +3885,7 @@
         <v>128701858</v>
       </c>
       <c r="B29" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>128701786</v>
       </c>
       <c r="B30" t="n">
-        <v>75027</v>
+        <v>75029</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>128701844</v>
       </c>
       <c r="B31" t="n">
-        <v>58093</v>
+        <v>58095</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>128701846</v>
       </c>
       <c r="B32" t="n">
-        <v>58400</v>
+        <v>58402</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 10555-2025 artfynd.xlsx
+++ b/artfynd/A 10555-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4385,6 +4385,126 @@
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>129874724</v>
+      </c>
+      <c r="B33" t="n">
+        <v>98780</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1258</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Hortkärr, Sm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>564906</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6443050</v>
+      </c>
+      <c r="S33" t="n">
+        <v>73</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Gärdserum</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>E-Åtv-0277</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Sammanställt från 34 rapporter</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Karin Nyström</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 10555-2025 artfynd.xlsx
+++ b/artfynd/A 10555-2025 artfynd.xlsx
@@ -4390,7 +4390,7 @@
         <v>129874724</v>
       </c>
       <c r="B33" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
